--- a/product_selector_out/STM32L100 value line - diff.xlsx
+++ b/product_selector_out/STM32L100 value line - diff.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Diff" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Diff'!$A$18:$E$35</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Diff'!$A$18:$E$32</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -33,7 +33,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -48,21 +48,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00DDEBF7"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00B7E1CD"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F4CCCC"/>
       </patternFill>
     </fill>
   </fills>
@@ -81,16 +66,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -456,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E35"/>
+  <dimension ref="A1:E32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -549,7 +531,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -609,7 +591,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -619,7 +601,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -629,7 +611,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="18">
@@ -943,22 +925,18 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>1.8</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1.65</t>
-        </is>
-      </c>
-      <c r="E31" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
@@ -970,100 +948,23 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>1.8</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1.65</t>
-        </is>
-      </c>
-      <c r="E32" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>STM32L100RC</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>1.8 (workbook and API agree)</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>1.65</t>
-        </is>
-      </c>
-      <c r="E33" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>STM32L100RC</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr"/>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E34" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>STM32L100RC</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr"/>
-      <c r="D35" t="inlineStr">
-        <is>
           <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
-      <c r="E35" s="3" t="inlineStr">
+      <c r="E32" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A18:E35"/>
+  <autoFilter ref="A18:E32"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/product_selector_out/STM32L100 value line - diff.xlsx
+++ b/product_selector_out/STM32L100 value line - diff.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>448</v>
+        <v>455</v>
       </c>
     </row>
     <row r="6">
@@ -521,7 +521,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -611,7 +611,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>434</v>
+        <v>441</v>
       </c>
     </row>
     <row r="18">
